--- a/aka-Tolob-files/отчёты/10-Анализ счёта/10_Анализ_счета_материалы_развернутый.xlsx
+++ b/aka-Tolob-files/отчёты/10-Анализ счёта/10_Анализ_счета_материалы_развернутый.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1-050126\документы\Отчёты\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\FEU\02-report-helpers\aka-Tolob-files\отчёты\10-Анализ счёта\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35706093-27F1-4AF0-8C6F-E32732AF004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8592" tabRatio="0"/>
   </bookViews>
   <sheets>
     <sheet name="TDSheet" sheetId="1" r:id="rId1"/>
@@ -100,7 +99,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -406,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -489,12 +488,252 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -506,261 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="6"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,23 +1102,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1170,23 +1137,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1362,7 +1312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -1391,73 +1341,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
     </row>
     <row r="2" spans="1:18" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="109" t="s">
+      <c r="A2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
     </row>
     <row r="3" spans="1:18" s="1" customFormat="1" ht="1.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
     </row>
     <row r="5" spans="1:18" s="1" customFormat="1" ht="1.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:18" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2"/>
@@ -1643,224 +1593,224 @@
     <row r="186" spans="1:15" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="187" spans="1:15" s="1" customFormat="1" ht="10.050000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="188" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="111" t="s">
+      <c r="A188" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B188" s="111"/>
-      <c r="C188" s="111"/>
-      <c r="D188" s="111"/>
-      <c r="E188" s="112" t="s">
+      <c r="B188" s="31"/>
+      <c r="C188" s="31"/>
+      <c r="D188" s="31"/>
+      <c r="E188" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F188" s="112"/>
-      <c r="G188" s="112"/>
-      <c r="H188" s="112" t="s">
+      <c r="F188" s="32"/>
+      <c r="G188" s="32"/>
+      <c r="H188" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="I188" s="112"/>
-      <c r="J188" s="112" t="s">
+      <c r="I188" s="32"/>
+      <c r="J188" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="K188" s="112"/>
-      <c r="L188" s="112"/>
-      <c r="M188" s="112" t="s">
+      <c r="K188" s="32"/>
+      <c r="L188" s="32"/>
+      <c r="M188" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="N188" s="112"/>
-      <c r="O188" s="112"/>
+      <c r="N188" s="32"/>
+      <c r="O188" s="32"/>
     </row>
     <row r="189" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="111" t="s">
+      <c r="A189" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B189" s="111"/>
-      <c r="C189" s="111"/>
-      <c r="D189" s="111"/>
-      <c r="E189" s="113"/>
-      <c r="F189" s="114"/>
-      <c r="G189" s="115"/>
-      <c r="H189" s="113"/>
-      <c r="I189" s="115"/>
-      <c r="J189" s="113"/>
-      <c r="K189" s="114"/>
-      <c r="L189" s="115"/>
-      <c r="M189" s="113"/>
-      <c r="N189" s="114"/>
-      <c r="O189" s="115"/>
+      <c r="B189" s="31"/>
+      <c r="C189" s="31"/>
+      <c r="D189" s="31"/>
+      <c r="E189" s="33"/>
+      <c r="F189" s="34"/>
+      <c r="G189" s="35"/>
+      <c r="H189" s="33"/>
+      <c r="I189" s="35"/>
+      <c r="J189" s="33"/>
+      <c r="K189" s="34"/>
+      <c r="L189" s="35"/>
+      <c r="M189" s="33"/>
+      <c r="N189" s="34"/>
+      <c r="O189" s="35"/>
     </row>
     <row r="190" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="111" t="s">
+      <c r="A190" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B190" s="111"/>
-      <c r="C190" s="111"/>
-      <c r="D190" s="111"/>
-      <c r="E190" s="116"/>
-      <c r="F190" s="117"/>
-      <c r="G190" s="118"/>
-      <c r="H190" s="116"/>
-      <c r="I190" s="118"/>
-      <c r="J190" s="116"/>
-      <c r="K190" s="117"/>
-      <c r="L190" s="118"/>
-      <c r="M190" s="116"/>
-      <c r="N190" s="117"/>
-      <c r="O190" s="118"/>
+      <c r="B190" s="31"/>
+      <c r="C190" s="31"/>
+      <c r="D190" s="31"/>
+      <c r="E190" s="36"/>
+      <c r="F190" s="37"/>
+      <c r="G190" s="38"/>
+      <c r="H190" s="36"/>
+      <c r="I190" s="38"/>
+      <c r="J190" s="36"/>
+      <c r="K190" s="37"/>
+      <c r="L190" s="38"/>
+      <c r="M190" s="36"/>
+      <c r="N190" s="37"/>
+      <c r="O190" s="38"/>
     </row>
     <row r="191" spans="1:15" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="95" t="s">
+      <c r="A191" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B191" s="95"/>
-      <c r="C191" s="95"/>
-      <c r="D191" s="95"/>
-      <c r="E191" s="99" t="s">
+      <c r="B191" s="39"/>
+      <c r="C191" s="39"/>
+      <c r="D191" s="39"/>
+      <c r="E191" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F191" s="99"/>
-      <c r="G191" s="99"/>
-      <c r="H191" s="103" t="s">
-        <v>5</v>
-      </c>
-      <c r="I191" s="103"/>
-      <c r="J191" s="104">
+      <c r="F191" s="43"/>
+      <c r="G191" s="43"/>
+      <c r="H191" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="I191" s="47"/>
+      <c r="J191" s="48">
         <f>J193+J205</f>
         <v>23550</v>
       </c>
-      <c r="K191" s="104"/>
-      <c r="L191" s="104"/>
+      <c r="K191" s="48"/>
+      <c r="L191" s="48"/>
       <c r="M191" s="2"/>
       <c r="N191" s="3"/>
       <c r="O191" s="4"/>
     </row>
     <row r="192" spans="1:15" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="96"/>
-      <c r="B192" s="97"/>
-      <c r="C192" s="97"/>
-      <c r="D192" s="98"/>
-      <c r="E192" s="100"/>
-      <c r="F192" s="101"/>
-      <c r="G192" s="102"/>
-      <c r="H192" s="103" t="s">
-        <v>10</v>
-      </c>
-      <c r="I192" s="103"/>
-      <c r="J192" s="104">
+      <c r="A192" s="40"/>
+      <c r="B192" s="41"/>
+      <c r="C192" s="41"/>
+      <c r="D192" s="42"/>
+      <c r="E192" s="44"/>
+      <c r="F192" s="45"/>
+      <c r="G192" s="46"/>
+      <c r="H192" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I192" s="47"/>
+      <c r="J192" s="48">
         <f>J194+J206</f>
         <v>127</v>
       </c>
-      <c r="K192" s="104"/>
-      <c r="L192" s="104"/>
+      <c r="K192" s="48"/>
+      <c r="L192" s="48"/>
       <c r="M192" s="2"/>
       <c r="N192" s="3"/>
       <c r="O192" s="4"/>
     </row>
     <row r="193" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="105" t="s">
+      <c r="A193" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="B193" s="106"/>
-      <c r="C193" s="106"/>
-      <c r="D193" s="107"/>
-      <c r="E193" s="84" t="s">
+      <c r="B193" s="50"/>
+      <c r="C193" s="50"/>
+      <c r="D193" s="51"/>
+      <c r="E193" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F193" s="84"/>
-      <c r="G193" s="84"/>
-      <c r="H193" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="I193" s="88"/>
-      <c r="J193" s="89">
+      <c r="F193" s="55"/>
+      <c r="G193" s="55"/>
+      <c r="H193" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I193" s="59"/>
+      <c r="J193" s="60">
         <v>150</v>
       </c>
-      <c r="K193" s="89"/>
-      <c r="L193" s="89"/>
+      <c r="K193" s="60"/>
+      <c r="L193" s="60"/>
       <c r="M193" s="5"/>
       <c r="N193" s="6"/>
       <c r="O193" s="7"/>
     </row>
     <row r="194" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="92"/>
-      <c r="B194" s="93"/>
-      <c r="C194" s="93"/>
-      <c r="D194" s="94"/>
-      <c r="E194" s="85"/>
-      <c r="F194" s="86"/>
-      <c r="G194" s="87"/>
-      <c r="H194" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="I194" s="88"/>
-      <c r="J194" s="90">
-        <v>10</v>
-      </c>
-      <c r="K194" s="90"/>
-      <c r="L194" s="90"/>
+      <c r="A194" s="52"/>
+      <c r="B194" s="53"/>
+      <c r="C194" s="53"/>
+      <c r="D194" s="54"/>
+      <c r="E194" s="56"/>
+      <c r="F194" s="57"/>
+      <c r="G194" s="58"/>
+      <c r="H194" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="I194" s="59"/>
+      <c r="J194" s="61">
+        <v>10</v>
+      </c>
+      <c r="K194" s="61"/>
+      <c r="L194" s="61"/>
       <c r="M194" s="5"/>
       <c r="N194" s="6"/>
       <c r="O194" s="7"/>
     </row>
     <row r="195" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A195" s="74" t="s">
+      <c r="A195" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B195" s="74"/>
-      <c r="C195" s="74"/>
-      <c r="D195" s="74"/>
-      <c r="E195" s="56" t="s">
+      <c r="B195" s="62"/>
+      <c r="C195" s="62"/>
+      <c r="D195" s="62"/>
+      <c r="E195" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F195" s="56"/>
-      <c r="G195" s="56"/>
-      <c r="H195" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I195" s="60"/>
-      <c r="J195" s="73">
+      <c r="F195" s="66"/>
+      <c r="G195" s="66"/>
+      <c r="H195" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I195" s="70"/>
+      <c r="J195" s="71">
         <v>150</v>
       </c>
-      <c r="K195" s="73"/>
-      <c r="L195" s="73"/>
+      <c r="K195" s="71"/>
+      <c r="L195" s="71"/>
       <c r="M195" s="8"/>
       <c r="N195" s="9"/>
       <c r="O195" s="10"/>
     </row>
     <row r="196" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A196" s="75"/>
-      <c r="B196" s="76"/>
-      <c r="C196" s="76"/>
-      <c r="D196" s="77"/>
-      <c r="E196" s="57"/>
-      <c r="F196" s="58"/>
-      <c r="G196" s="59"/>
-      <c r="H196" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I196" s="60"/>
-      <c r="J196" s="78">
-        <v>10</v>
-      </c>
-      <c r="K196" s="78"/>
-      <c r="L196" s="78"/>
+      <c r="A196" s="63"/>
+      <c r="B196" s="64"/>
+      <c r="C196" s="64"/>
+      <c r="D196" s="65"/>
+      <c r="E196" s="67"/>
+      <c r="F196" s="68"/>
+      <c r="G196" s="69"/>
+      <c r="H196" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I196" s="70"/>
+      <c r="J196" s="72">
+        <v>10</v>
+      </c>
+      <c r="K196" s="72"/>
+      <c r="L196" s="72"/>
       <c r="M196" s="8"/>
       <c r="N196" s="9"/>
       <c r="O196" s="10"/>
     </row>
     <row r="197" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A197" s="52"/>
-      <c r="B197" s="52"/>
-      <c r="C197" s="52"/>
-      <c r="D197" s="52"/>
-      <c r="E197" s="56" t="s">
+      <c r="A197" s="73"/>
+      <c r="B197" s="73"/>
+      <c r="C197" s="73"/>
+      <c r="D197" s="73"/>
+      <c r="E197" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F197" s="56"/>
-      <c r="G197" s="56"/>
-      <c r="H197" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I197" s="60"/>
+      <c r="F197" s="66"/>
+      <c r="G197" s="66"/>
+      <c r="H197" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I197" s="70"/>
       <c r="J197" s="11"/>
       <c r="K197" s="12"/>
       <c r="L197" s="13"/>
@@ -1869,17 +1819,17 @@
       <c r="O197" s="13"/>
     </row>
     <row r="198" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A198" s="53"/>
-      <c r="B198" s="54"/>
-      <c r="C198" s="54"/>
-      <c r="D198" s="55"/>
-      <c r="E198" s="57"/>
-      <c r="F198" s="58"/>
-      <c r="G198" s="59"/>
-      <c r="H198" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I198" s="60"/>
+      <c r="A198" s="74"/>
+      <c r="B198" s="75"/>
+      <c r="C198" s="75"/>
+      <c r="D198" s="76"/>
+      <c r="E198" s="67"/>
+      <c r="F198" s="68"/>
+      <c r="G198" s="69"/>
+      <c r="H198" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I198" s="70"/>
       <c r="J198" s="11"/>
       <c r="K198" s="12"/>
       <c r="L198" s="13"/>
@@ -1888,63 +1838,63 @@
       <c r="O198" s="13"/>
     </row>
     <row r="199" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A199" s="52"/>
-      <c r="B199" s="52"/>
-      <c r="C199" s="52"/>
-      <c r="D199" s="52"/>
-      <c r="E199" s="56" t="s">
+      <c r="A199" s="73"/>
+      <c r="B199" s="73"/>
+      <c r="C199" s="73"/>
+      <c r="D199" s="73"/>
+      <c r="E199" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F199" s="56"/>
-      <c r="G199" s="56"/>
-      <c r="H199" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I199" s="60"/>
-      <c r="J199" s="73">
+      <c r="F199" s="66"/>
+      <c r="G199" s="66"/>
+      <c r="H199" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I199" s="70"/>
+      <c r="J199" s="71">
         <v>150</v>
       </c>
-      <c r="K199" s="73"/>
-      <c r="L199" s="73"/>
+      <c r="K199" s="71"/>
+      <c r="L199" s="71"/>
       <c r="M199" s="8"/>
       <c r="N199" s="9"/>
       <c r="O199" s="10"/>
     </row>
     <row r="200" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A200" s="53"/>
-      <c r="B200" s="54"/>
-      <c r="C200" s="54"/>
-      <c r="D200" s="55"/>
-      <c r="E200" s="57"/>
-      <c r="F200" s="58"/>
-      <c r="G200" s="59"/>
-      <c r="H200" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I200" s="60"/>
-      <c r="J200" s="78">
-        <v>10</v>
-      </c>
-      <c r="K200" s="78"/>
-      <c r="L200" s="78"/>
+      <c r="A200" s="74"/>
+      <c r="B200" s="75"/>
+      <c r="C200" s="75"/>
+      <c r="D200" s="76"/>
+      <c r="E200" s="67"/>
+      <c r="F200" s="68"/>
+      <c r="G200" s="69"/>
+      <c r="H200" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I200" s="70"/>
+      <c r="J200" s="72">
+        <v>10</v>
+      </c>
+      <c r="K200" s="72"/>
+      <c r="L200" s="72"/>
       <c r="M200" s="8"/>
       <c r="N200" s="9"/>
       <c r="O200" s="10"/>
     </row>
     <row r="201" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="80"/>
-      <c r="B201" s="80"/>
-      <c r="C201" s="80"/>
-      <c r="D201" s="80"/>
-      <c r="E201" s="84" t="s">
+      <c r="A201" s="77"/>
+      <c r="B201" s="77"/>
+      <c r="C201" s="77"/>
+      <c r="D201" s="77"/>
+      <c r="E201" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="F201" s="84"/>
-      <c r="G201" s="84"/>
-      <c r="H201" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="I201" s="88"/>
+      <c r="F201" s="55"/>
+      <c r="G201" s="55"/>
+      <c r="H201" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I201" s="59"/>
       <c r="J201" s="14"/>
       <c r="K201" s="15"/>
       <c r="L201" s="16"/>
@@ -1953,17 +1903,17 @@
       <c r="O201" s="16"/>
     </row>
     <row r="202" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="81"/>
-      <c r="B202" s="82"/>
-      <c r="C202" s="82"/>
-      <c r="D202" s="83"/>
-      <c r="E202" s="85"/>
-      <c r="F202" s="86"/>
-      <c r="G202" s="87"/>
-      <c r="H202" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="I202" s="88"/>
+      <c r="A202" s="78"/>
+      <c r="B202" s="79"/>
+      <c r="C202" s="79"/>
+      <c r="D202" s="80"/>
+      <c r="E202" s="56"/>
+      <c r="F202" s="57"/>
+      <c r="G202" s="58"/>
+      <c r="H202" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="I202" s="59"/>
       <c r="J202" s="14"/>
       <c r="K202" s="15"/>
       <c r="L202" s="16"/>
@@ -1972,159 +1922,159 @@
       <c r="O202" s="16"/>
     </row>
     <row r="203" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="80"/>
-      <c r="B203" s="80"/>
-      <c r="C203" s="80"/>
-      <c r="D203" s="80"/>
-      <c r="E203" s="84" t="s">
+      <c r="A203" s="77"/>
+      <c r="B203" s="77"/>
+      <c r="C203" s="77"/>
+      <c r="D203" s="77"/>
+      <c r="E203" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="F203" s="84"/>
-      <c r="G203" s="84"/>
-      <c r="H203" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="I203" s="88"/>
-      <c r="J203" s="89">
+      <c r="F203" s="55"/>
+      <c r="G203" s="55"/>
+      <c r="H203" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I203" s="59"/>
+      <c r="J203" s="60">
         <f>J199</f>
         <v>150</v>
       </c>
-      <c r="K203" s="89"/>
-      <c r="L203" s="89"/>
+      <c r="K203" s="60"/>
+      <c r="L203" s="60"/>
       <c r="M203" s="5"/>
       <c r="N203" s="6"/>
       <c r="O203" s="7"/>
     </row>
     <row r="204" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="81"/>
-      <c r="B204" s="82"/>
-      <c r="C204" s="82"/>
-      <c r="D204" s="83"/>
-      <c r="E204" s="85"/>
-      <c r="F204" s="86"/>
-      <c r="G204" s="87"/>
-      <c r="H204" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="I204" s="88"/>
-      <c r="J204" s="90">
+      <c r="A204" s="78"/>
+      <c r="B204" s="79"/>
+      <c r="C204" s="79"/>
+      <c r="D204" s="80"/>
+      <c r="E204" s="56"/>
+      <c r="F204" s="57"/>
+      <c r="G204" s="58"/>
+      <c r="H204" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="I204" s="59"/>
+      <c r="J204" s="61">
         <f>J200</f>
         <v>10</v>
       </c>
-      <c r="K204" s="90"/>
-      <c r="L204" s="90"/>
+      <c r="K204" s="61"/>
+      <c r="L204" s="61"/>
       <c r="M204" s="5"/>
       <c r="N204" s="6"/>
       <c r="O204" s="7"/>
     </row>
     <row r="205" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="91" t="s">
+      <c r="A205" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="B205" s="91"/>
-      <c r="C205" s="91"/>
-      <c r="D205" s="91"/>
-      <c r="E205" s="84" t="s">
+      <c r="B205" s="81"/>
+      <c r="C205" s="81"/>
+      <c r="D205" s="81"/>
+      <c r="E205" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="F205" s="84"/>
-      <c r="G205" s="84"/>
-      <c r="H205" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="I205" s="88"/>
-      <c r="J205" s="89">
+      <c r="F205" s="55"/>
+      <c r="G205" s="55"/>
+      <c r="H205" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I205" s="59"/>
+      <c r="J205" s="60">
         <f>J207+J213+J221+J227</f>
         <v>23400</v>
       </c>
-      <c r="K205" s="89"/>
-      <c r="L205" s="89"/>
+      <c r="K205" s="60"/>
+      <c r="L205" s="60"/>
       <c r="M205" s="5"/>
       <c r="N205" s="6"/>
       <c r="O205" s="7"/>
     </row>
     <row r="206" spans="1:15" ht="10.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="92"/>
-      <c r="B206" s="93"/>
-      <c r="C206" s="93"/>
-      <c r="D206" s="94"/>
-      <c r="E206" s="85"/>
-      <c r="F206" s="86"/>
-      <c r="G206" s="87"/>
-      <c r="H206" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="I206" s="88"/>
-      <c r="J206" s="89">
+      <c r="A206" s="52"/>
+      <c r="B206" s="53"/>
+      <c r="C206" s="53"/>
+      <c r="D206" s="54"/>
+      <c r="E206" s="56"/>
+      <c r="F206" s="57"/>
+      <c r="G206" s="58"/>
+      <c r="H206" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="I206" s="59"/>
+      <c r="J206" s="60">
         <f>J208+J214+J222+J228</f>
         <v>117</v>
       </c>
-      <c r="K206" s="89"/>
-      <c r="L206" s="89"/>
+      <c r="K206" s="60"/>
+      <c r="L206" s="60"/>
       <c r="M206" s="5"/>
       <c r="N206" s="6"/>
       <c r="O206" s="7"/>
     </row>
     <row r="207" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A207" s="74" t="s">
+      <c r="A207" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B207" s="74"/>
-      <c r="C207" s="74"/>
-      <c r="D207" s="74"/>
-      <c r="E207" s="56" t="s">
+      <c r="B207" s="62"/>
+      <c r="C207" s="62"/>
+      <c r="D207" s="62"/>
+      <c r="E207" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F207" s="56"/>
-      <c r="G207" s="56"/>
-      <c r="H207" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I207" s="60"/>
-      <c r="J207" s="73">
+      <c r="F207" s="66"/>
+      <c r="G207" s="66"/>
+      <c r="H207" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I207" s="70"/>
+      <c r="J207" s="71">
         <v>2000</v>
       </c>
-      <c r="K207" s="73"/>
-      <c r="L207" s="73"/>
+      <c r="K207" s="71"/>
+      <c r="L207" s="71"/>
       <c r="M207" s="8"/>
       <c r="N207" s="9"/>
       <c r="O207" s="10"/>
     </row>
     <row r="208" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A208" s="75"/>
-      <c r="B208" s="76"/>
-      <c r="C208" s="76"/>
-      <c r="D208" s="77"/>
-      <c r="E208" s="57"/>
-      <c r="F208" s="58"/>
-      <c r="G208" s="59"/>
-      <c r="H208" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I208" s="60"/>
-      <c r="J208" s="79">
-        <v>10</v>
-      </c>
-      <c r="K208" s="79"/>
-      <c r="L208" s="79"/>
+      <c r="A208" s="63"/>
+      <c r="B208" s="64"/>
+      <c r="C208" s="64"/>
+      <c r="D208" s="65"/>
+      <c r="E208" s="67"/>
+      <c r="F208" s="68"/>
+      <c r="G208" s="69"/>
+      <c r="H208" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I208" s="70"/>
+      <c r="J208" s="82">
+        <v>10</v>
+      </c>
+      <c r="K208" s="82"/>
+      <c r="L208" s="82"/>
       <c r="M208" s="8"/>
       <c r="N208" s="9"/>
       <c r="O208" s="10"/>
     </row>
     <row r="209" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A209" s="52"/>
-      <c r="B209" s="52"/>
-      <c r="C209" s="52"/>
-      <c r="D209" s="52"/>
-      <c r="E209" s="56" t="s">
+      <c r="A209" s="73"/>
+      <c r="B209" s="73"/>
+      <c r="C209" s="73"/>
+      <c r="D209" s="73"/>
+      <c r="E209" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F209" s="56"/>
-      <c r="G209" s="56"/>
-      <c r="H209" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I209" s="60"/>
+      <c r="F209" s="66"/>
+      <c r="G209" s="66"/>
+      <c r="H209" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I209" s="70"/>
       <c r="J209" s="11"/>
       <c r="K209" s="12"/>
       <c r="L209" s="13"/>
@@ -2133,17 +2083,17 @@
       <c r="O209" s="13"/>
     </row>
     <row r="210" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A210" s="53"/>
-      <c r="B210" s="54"/>
-      <c r="C210" s="54"/>
-      <c r="D210" s="55"/>
-      <c r="E210" s="57"/>
-      <c r="F210" s="58"/>
-      <c r="G210" s="59"/>
-      <c r="H210" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I210" s="60"/>
+      <c r="A210" s="74"/>
+      <c r="B210" s="75"/>
+      <c r="C210" s="75"/>
+      <c r="D210" s="76"/>
+      <c r="E210" s="67"/>
+      <c r="F210" s="68"/>
+      <c r="G210" s="69"/>
+      <c r="H210" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I210" s="70"/>
       <c r="J210" s="11"/>
       <c r="K210" s="12"/>
       <c r="L210" s="13"/>
@@ -2152,289 +2102,289 @@
       <c r="O210" s="13"/>
     </row>
     <row r="211" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A211" s="52"/>
-      <c r="B211" s="52"/>
-      <c r="C211" s="52"/>
-      <c r="D211" s="52"/>
-      <c r="E211" s="56" t="s">
+      <c r="A211" s="73"/>
+      <c r="B211" s="73"/>
+      <c r="C211" s="73"/>
+      <c r="D211" s="73"/>
+      <c r="E211" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F211" s="56"/>
-      <c r="G211" s="56"/>
-      <c r="H211" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I211" s="60"/>
-      <c r="J211" s="73">
+      <c r="F211" s="66"/>
+      <c r="G211" s="66"/>
+      <c r="H211" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I211" s="70"/>
+      <c r="J211" s="71">
         <v>2000</v>
       </c>
-      <c r="K211" s="73"/>
-      <c r="L211" s="73"/>
+      <c r="K211" s="71"/>
+      <c r="L211" s="71"/>
       <c r="M211" s="8"/>
       <c r="N211" s="9"/>
       <c r="O211" s="10"/>
     </row>
     <row r="212" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A212" s="53"/>
-      <c r="B212" s="54"/>
-      <c r="C212" s="54"/>
-      <c r="D212" s="55"/>
-      <c r="E212" s="57"/>
-      <c r="F212" s="58"/>
-      <c r="G212" s="59"/>
-      <c r="H212" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I212" s="60"/>
-      <c r="J212" s="79">
-        <v>10</v>
-      </c>
-      <c r="K212" s="79"/>
-      <c r="L212" s="79"/>
+      <c r="A212" s="74"/>
+      <c r="B212" s="75"/>
+      <c r="C212" s="75"/>
+      <c r="D212" s="76"/>
+      <c r="E212" s="67"/>
+      <c r="F212" s="68"/>
+      <c r="G212" s="69"/>
+      <c r="H212" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I212" s="70"/>
+      <c r="J212" s="82">
+        <v>10</v>
+      </c>
+      <c r="K212" s="82"/>
+      <c r="L212" s="82"/>
       <c r="M212" s="8"/>
       <c r="N212" s="9"/>
       <c r="O212" s="10"/>
     </row>
     <row r="213" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A213" s="74" t="s">
+      <c r="A213" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B213" s="74"/>
-      <c r="C213" s="74"/>
-      <c r="D213" s="74"/>
-      <c r="E213" s="56" t="s">
+      <c r="B213" s="62"/>
+      <c r="C213" s="62"/>
+      <c r="D213" s="62"/>
+      <c r="E213" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F213" s="56"/>
-      <c r="G213" s="56"/>
-      <c r="H213" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I213" s="60"/>
-      <c r="J213" s="73">
+      <c r="F213" s="66"/>
+      <c r="G213" s="66"/>
+      <c r="H213" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I213" s="70"/>
+      <c r="J213" s="71">
         <v>1000</v>
       </c>
-      <c r="K213" s="73"/>
-      <c r="L213" s="73"/>
+      <c r="K213" s="71"/>
+      <c r="L213" s="71"/>
       <c r="M213" s="8"/>
       <c r="N213" s="9"/>
       <c r="O213" s="10"/>
     </row>
     <row r="214" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A214" s="75"/>
-      <c r="B214" s="76"/>
-      <c r="C214" s="76"/>
-      <c r="D214" s="77"/>
-      <c r="E214" s="57"/>
-      <c r="F214" s="58"/>
-      <c r="G214" s="59"/>
-      <c r="H214" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I214" s="60"/>
-      <c r="J214" s="79">
-        <v>5</v>
-      </c>
-      <c r="K214" s="79"/>
-      <c r="L214" s="79"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="64"/>
+      <c r="C214" s="64"/>
+      <c r="D214" s="65"/>
+      <c r="E214" s="67"/>
+      <c r="F214" s="68"/>
+      <c r="G214" s="69"/>
+      <c r="H214" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I214" s="70"/>
+      <c r="J214" s="82">
+        <v>5</v>
+      </c>
+      <c r="K214" s="82"/>
+      <c r="L214" s="82"/>
       <c r="M214" s="8"/>
       <c r="N214" s="9"/>
       <c r="O214" s="10"/>
     </row>
     <row r="215" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A215" s="62"/>
-      <c r="B215" s="62"/>
-      <c r="C215" s="62"/>
-      <c r="D215" s="62"/>
-      <c r="E215" s="66" t="s">
+      <c r="A215" s="83"/>
+      <c r="B215" s="83"/>
+      <c r="C215" s="83"/>
+      <c r="D215" s="83"/>
+      <c r="E215" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="F215" s="66"/>
-      <c r="G215" s="66"/>
-      <c r="H215" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="I215" s="70"/>
+      <c r="F215" s="87"/>
+      <c r="G215" s="87"/>
+      <c r="H215" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="I215" s="91"/>
       <c r="J215" s="17"/>
       <c r="K215" s="18"/>
       <c r="L215" s="19"/>
-      <c r="M215" s="71">
+      <c r="M215" s="92">
         <v>1000</v>
       </c>
-      <c r="N215" s="71"/>
-      <c r="O215" s="71"/>
+      <c r="N215" s="92"/>
+      <c r="O215" s="92"/>
     </row>
     <row r="216" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A216" s="63"/>
-      <c r="B216" s="64"/>
-      <c r="C216" s="64"/>
-      <c r="D216" s="65"/>
-      <c r="E216" s="67"/>
-      <c r="F216" s="68"/>
-      <c r="G216" s="69"/>
-      <c r="H216" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="I216" s="70"/>
+      <c r="A216" s="84"/>
+      <c r="B216" s="85"/>
+      <c r="C216" s="85"/>
+      <c r="D216" s="86"/>
+      <c r="E216" s="88"/>
+      <c r="F216" s="89"/>
+      <c r="G216" s="90"/>
+      <c r="H216" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="I216" s="91"/>
       <c r="J216" s="17"/>
       <c r="K216" s="18"/>
       <c r="L216" s="19"/>
-      <c r="M216" s="72">
-        <v>5</v>
-      </c>
-      <c r="N216" s="72"/>
-      <c r="O216" s="72"/>
+      <c r="M216" s="93">
+        <v>5</v>
+      </c>
+      <c r="N216" s="93"/>
+      <c r="O216" s="93"/>
     </row>
     <row r="217" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A217" s="52"/>
-      <c r="B217" s="52"/>
-      <c r="C217" s="52"/>
-      <c r="D217" s="52"/>
-      <c r="E217" s="56" t="s">
+      <c r="A217" s="73"/>
+      <c r="B217" s="73"/>
+      <c r="C217" s="73"/>
+      <c r="D217" s="73"/>
+      <c r="E217" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F217" s="56"/>
-      <c r="G217" s="56"/>
-      <c r="H217" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I217" s="60"/>
+      <c r="F217" s="66"/>
+      <c r="G217" s="66"/>
+      <c r="H217" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I217" s="70"/>
       <c r="J217" s="8"/>
       <c r="K217" s="9"/>
       <c r="L217" s="10"/>
-      <c r="M217" s="73">
+      <c r="M217" s="71">
         <v>1000</v>
       </c>
-      <c r="N217" s="73"/>
-      <c r="O217" s="73"/>
+      <c r="N217" s="71"/>
+      <c r="O217" s="71"/>
     </row>
     <row r="218" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A218" s="53"/>
-      <c r="B218" s="54"/>
-      <c r="C218" s="54"/>
-      <c r="D218" s="55"/>
-      <c r="E218" s="57"/>
-      <c r="F218" s="58"/>
-      <c r="G218" s="59"/>
-      <c r="H218" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I218" s="60"/>
+      <c r="A218" s="74"/>
+      <c r="B218" s="75"/>
+      <c r="C218" s="75"/>
+      <c r="D218" s="76"/>
+      <c r="E218" s="67"/>
+      <c r="F218" s="68"/>
+      <c r="G218" s="69"/>
+      <c r="H218" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I218" s="70"/>
       <c r="J218" s="8"/>
       <c r="K218" s="9"/>
       <c r="L218" s="10"/>
-      <c r="M218" s="78">
-        <v>5</v>
-      </c>
-      <c r="N218" s="78"/>
-      <c r="O218" s="78"/>
+      <c r="M218" s="72">
+        <v>5</v>
+      </c>
+      <c r="N218" s="72"/>
+      <c r="O218" s="72"/>
     </row>
     <row r="219" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A219" s="52"/>
-      <c r="B219" s="52"/>
-      <c r="C219" s="52"/>
-      <c r="D219" s="52"/>
-      <c r="E219" s="56" t="s">
+      <c r="A219" s="73"/>
+      <c r="B219" s="73"/>
+      <c r="C219" s="73"/>
+      <c r="D219" s="73"/>
+      <c r="E219" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F219" s="56"/>
-      <c r="G219" s="56"/>
-      <c r="H219" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I219" s="60"/>
-      <c r="J219" s="73">
+      <c r="F219" s="66"/>
+      <c r="G219" s="66"/>
+      <c r="H219" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I219" s="70"/>
+      <c r="J219" s="71">
         <f>J213-M217</f>
         <v>0</v>
       </c>
-      <c r="K219" s="73"/>
-      <c r="L219" s="73"/>
+      <c r="K219" s="71"/>
+      <c r="L219" s="71"/>
       <c r="M219" s="8"/>
       <c r="N219" s="9"/>
       <c r="O219" s="10"/>
     </row>
     <row r="220" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A220" s="53"/>
-      <c r="B220" s="54"/>
-      <c r="C220" s="54"/>
-      <c r="D220" s="55"/>
-      <c r="E220" s="57"/>
-      <c r="F220" s="58"/>
-      <c r="G220" s="59"/>
-      <c r="H220" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I220" s="60"/>
-      <c r="J220" s="79">
+      <c r="A220" s="74"/>
+      <c r="B220" s="75"/>
+      <c r="C220" s="75"/>
+      <c r="D220" s="76"/>
+      <c r="E220" s="67"/>
+      <c r="F220" s="68"/>
+      <c r="G220" s="69"/>
+      <c r="H220" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I220" s="70"/>
+      <c r="J220" s="82">
         <f>J214-M218</f>
         <v>0</v>
       </c>
-      <c r="K220" s="79"/>
-      <c r="L220" s="79"/>
+      <c r="K220" s="82"/>
+      <c r="L220" s="82"/>
       <c r="M220" s="8"/>
       <c r="N220" s="9"/>
       <c r="O220" s="10"/>
     </row>
     <row r="221" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A221" s="74" t="s">
+      <c r="A221" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B221" s="74"/>
-      <c r="C221" s="74"/>
-      <c r="D221" s="74"/>
-      <c r="E221" s="56" t="s">
+      <c r="B221" s="62"/>
+      <c r="C221" s="62"/>
+      <c r="D221" s="62"/>
+      <c r="E221" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F221" s="56"/>
-      <c r="G221" s="56"/>
-      <c r="H221" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I221" s="60"/>
-      <c r="J221" s="73">
+      <c r="F221" s="66"/>
+      <c r="G221" s="66"/>
+      <c r="H221" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I221" s="70"/>
+      <c r="J221" s="71">
         <v>400</v>
       </c>
-      <c r="K221" s="73"/>
-      <c r="L221" s="73"/>
+      <c r="K221" s="71"/>
+      <c r="L221" s="71"/>
       <c r="M221" s="8"/>
       <c r="N221" s="9"/>
       <c r="O221" s="10"/>
     </row>
     <row r="222" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A222" s="75"/>
-      <c r="B222" s="76"/>
-      <c r="C222" s="76"/>
-      <c r="D222" s="77"/>
-      <c r="E222" s="57"/>
-      <c r="F222" s="58"/>
-      <c r="G222" s="59"/>
-      <c r="H222" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I222" s="60"/>
-      <c r="J222" s="78">
+      <c r="A222" s="63"/>
+      <c r="B222" s="64"/>
+      <c r="C222" s="64"/>
+      <c r="D222" s="65"/>
+      <c r="E222" s="67"/>
+      <c r="F222" s="68"/>
+      <c r="G222" s="69"/>
+      <c r="H222" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I222" s="70"/>
+      <c r="J222" s="72">
         <v>2</v>
       </c>
-      <c r="K222" s="78"/>
-      <c r="L222" s="78"/>
+      <c r="K222" s="72"/>
+      <c r="L222" s="72"/>
       <c r="M222" s="8"/>
       <c r="N222" s="9"/>
       <c r="O222" s="10"/>
     </row>
     <row r="223" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A223" s="52"/>
-      <c r="B223" s="52"/>
-      <c r="C223" s="52"/>
-      <c r="D223" s="52"/>
-      <c r="E223" s="56" t="s">
+      <c r="A223" s="73"/>
+      <c r="B223" s="73"/>
+      <c r="C223" s="73"/>
+      <c r="D223" s="73"/>
+      <c r="E223" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F223" s="56"/>
-      <c r="G223" s="56"/>
-      <c r="H223" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I223" s="60"/>
+      <c r="F223" s="66"/>
+      <c r="G223" s="66"/>
+      <c r="H223" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I223" s="70"/>
       <c r="J223" s="11"/>
       <c r="K223" s="12"/>
       <c r="L223" s="13"/>
@@ -2443,17 +2393,17 @@
       <c r="O223" s="13"/>
     </row>
     <row r="224" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A224" s="53"/>
-      <c r="B224" s="54"/>
-      <c r="C224" s="54"/>
-      <c r="D224" s="55"/>
-      <c r="E224" s="57"/>
-      <c r="F224" s="58"/>
-      <c r="G224" s="59"/>
-      <c r="H224" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I224" s="60"/>
+      <c r="A224" s="74"/>
+      <c r="B224" s="75"/>
+      <c r="C224" s="75"/>
+      <c r="D224" s="76"/>
+      <c r="E224" s="67"/>
+      <c r="F224" s="68"/>
+      <c r="G224" s="69"/>
+      <c r="H224" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I224" s="70"/>
       <c r="J224" s="11"/>
       <c r="K224" s="12"/>
       <c r="L224" s="13"/>
@@ -2462,278 +2412,278 @@
       <c r="O224" s="13"/>
     </row>
     <row r="225" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A225" s="52"/>
-      <c r="B225" s="52"/>
-      <c r="C225" s="52"/>
-      <c r="D225" s="52"/>
-      <c r="E225" s="56" t="s">
+      <c r="A225" s="73"/>
+      <c r="B225" s="73"/>
+      <c r="C225" s="73"/>
+      <c r="D225" s="73"/>
+      <c r="E225" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F225" s="56"/>
-      <c r="G225" s="56"/>
-      <c r="H225" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I225" s="60"/>
-      <c r="J225" s="73">
+      <c r="F225" s="66"/>
+      <c r="G225" s="66"/>
+      <c r="H225" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I225" s="70"/>
+      <c r="J225" s="71">
         <v>400</v>
       </c>
-      <c r="K225" s="73"/>
-      <c r="L225" s="73"/>
+      <c r="K225" s="71"/>
+      <c r="L225" s="71"/>
       <c r="M225" s="8"/>
       <c r="N225" s="9"/>
       <c r="O225" s="10"/>
     </row>
     <row r="226" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A226" s="53"/>
-      <c r="B226" s="54"/>
-      <c r="C226" s="54"/>
-      <c r="D226" s="55"/>
-      <c r="E226" s="57"/>
-      <c r="F226" s="58"/>
-      <c r="G226" s="59"/>
-      <c r="H226" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I226" s="60"/>
-      <c r="J226" s="78">
+      <c r="A226" s="74"/>
+      <c r="B226" s="75"/>
+      <c r="C226" s="75"/>
+      <c r="D226" s="76"/>
+      <c r="E226" s="67"/>
+      <c r="F226" s="68"/>
+      <c r="G226" s="69"/>
+      <c r="H226" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I226" s="70"/>
+      <c r="J226" s="72">
         <v>2</v>
       </c>
-      <c r="K226" s="78"/>
-      <c r="L226" s="78"/>
+      <c r="K226" s="72"/>
+      <c r="L226" s="72"/>
       <c r="M226" s="8"/>
       <c r="N226" s="9"/>
       <c r="O226" s="10"/>
     </row>
     <row r="227" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A227" s="74" t="s">
+      <c r="A227" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B227" s="74"/>
-      <c r="C227" s="74"/>
-      <c r="D227" s="74"/>
-      <c r="E227" s="56" t="s">
+      <c r="B227" s="62"/>
+      <c r="C227" s="62"/>
+      <c r="D227" s="62"/>
+      <c r="E227" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="F227" s="56"/>
-      <c r="G227" s="56"/>
-      <c r="H227" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I227" s="60"/>
-      <c r="J227" s="61">
+      <c r="F227" s="66"/>
+      <c r="G227" s="66"/>
+      <c r="H227" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I227" s="70"/>
+      <c r="J227" s="94">
         <v>20000</v>
       </c>
-      <c r="K227" s="61"/>
-      <c r="L227" s="61"/>
+      <c r="K227" s="94"/>
+      <c r="L227" s="94"/>
       <c r="M227" s="8"/>
       <c r="N227" s="9"/>
       <c r="O227" s="10"/>
     </row>
     <row r="228" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A228" s="75"/>
-      <c r="B228" s="76"/>
-      <c r="C228" s="76"/>
-      <c r="D228" s="77"/>
-      <c r="E228" s="57"/>
-      <c r="F228" s="58"/>
-      <c r="G228" s="59"/>
-      <c r="H228" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I228" s="60"/>
-      <c r="J228" s="78">
+      <c r="A228" s="63"/>
+      <c r="B228" s="64"/>
+      <c r="C228" s="64"/>
+      <c r="D228" s="65"/>
+      <c r="E228" s="67"/>
+      <c r="F228" s="68"/>
+      <c r="G228" s="69"/>
+      <c r="H228" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I228" s="70"/>
+      <c r="J228" s="72">
         <v>100</v>
       </c>
-      <c r="K228" s="78"/>
-      <c r="L228" s="78"/>
+      <c r="K228" s="72"/>
+      <c r="L228" s="72"/>
       <c r="M228" s="8"/>
       <c r="N228" s="9"/>
       <c r="O228" s="10"/>
     </row>
     <row r="229" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A229" s="62"/>
-      <c r="B229" s="62"/>
-      <c r="C229" s="62"/>
-      <c r="D229" s="62"/>
-      <c r="E229" s="66" t="s">
+      <c r="A229" s="83"/>
+      <c r="B229" s="83"/>
+      <c r="C229" s="83"/>
+      <c r="D229" s="83"/>
+      <c r="E229" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="F229" s="66"/>
-      <c r="G229" s="66"/>
-      <c r="H229" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="I229" s="70"/>
-      <c r="J229" s="71">
+      <c r="F229" s="87"/>
+      <c r="G229" s="87"/>
+      <c r="H229" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="I229" s="91"/>
+      <c r="J229" s="92">
         <f>M215</f>
         <v>1000</v>
       </c>
-      <c r="K229" s="71"/>
-      <c r="L229" s="71"/>
+      <c r="K229" s="92"/>
+      <c r="L229" s="92"/>
       <c r="M229" s="17"/>
       <c r="N229" s="18"/>
       <c r="O229" s="19"/>
     </row>
     <row r="230" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A230" s="63"/>
-      <c r="B230" s="64"/>
-      <c r="C230" s="64"/>
-      <c r="D230" s="65"/>
-      <c r="E230" s="67"/>
-      <c r="F230" s="68"/>
-      <c r="G230" s="69"/>
-      <c r="H230" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="I230" s="70"/>
-      <c r="J230" s="72">
-        <v>5</v>
-      </c>
-      <c r="K230" s="72"/>
-      <c r="L230" s="72"/>
+      <c r="A230" s="84"/>
+      <c r="B230" s="85"/>
+      <c r="C230" s="85"/>
+      <c r="D230" s="86"/>
+      <c r="E230" s="88"/>
+      <c r="F230" s="89"/>
+      <c r="G230" s="90"/>
+      <c r="H230" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="I230" s="91"/>
+      <c r="J230" s="93">
+        <v>5</v>
+      </c>
+      <c r="K230" s="93"/>
+      <c r="L230" s="93"/>
       <c r="M230" s="17"/>
       <c r="N230" s="18"/>
       <c r="O230" s="19"/>
     </row>
     <row r="231" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A231" s="62"/>
-      <c r="B231" s="62"/>
-      <c r="C231" s="62"/>
-      <c r="D231" s="62"/>
-      <c r="E231" s="66" t="s">
+      <c r="A231" s="83"/>
+      <c r="B231" s="83"/>
+      <c r="C231" s="83"/>
+      <c r="D231" s="83"/>
+      <c r="E231" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="F231" s="66"/>
-      <c r="G231" s="66"/>
-      <c r="H231" s="70" t="s">
-        <v>5</v>
-      </c>
-      <c r="I231" s="70"/>
+      <c r="F231" s="87"/>
+      <c r="G231" s="87"/>
+      <c r="H231" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="I231" s="91"/>
       <c r="J231" s="17"/>
       <c r="K231" s="18"/>
       <c r="L231" s="19"/>
-      <c r="M231" s="71">
+      <c r="M231" s="92">
         <v>200</v>
       </c>
-      <c r="N231" s="71"/>
-      <c r="O231" s="71"/>
+      <c r="N231" s="92"/>
+      <c r="O231" s="92"/>
     </row>
     <row r="232" spans="1:15" ht="10.95" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
-      <c r="A232" s="63"/>
-      <c r="B232" s="64"/>
-      <c r="C232" s="64"/>
-      <c r="D232" s="65"/>
-      <c r="E232" s="67"/>
-      <c r="F232" s="68"/>
-      <c r="G232" s="69"/>
-      <c r="H232" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="I232" s="70"/>
+      <c r="A232" s="84"/>
+      <c r="B232" s="85"/>
+      <c r="C232" s="85"/>
+      <c r="D232" s="86"/>
+      <c r="E232" s="88"/>
+      <c r="F232" s="89"/>
+      <c r="G232" s="90"/>
+      <c r="H232" s="91" t="s">
+        <v>10</v>
+      </c>
+      <c r="I232" s="91"/>
       <c r="J232" s="17"/>
       <c r="K232" s="18"/>
       <c r="L232" s="19"/>
-      <c r="M232" s="72">
+      <c r="M232" s="93">
         <v>1</v>
       </c>
-      <c r="N232" s="72"/>
-      <c r="O232" s="72"/>
+      <c r="N232" s="93"/>
+      <c r="O232" s="93"/>
     </row>
     <row r="233" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A233" s="52"/>
-      <c r="B233" s="52"/>
-      <c r="C233" s="52"/>
-      <c r="D233" s="52"/>
-      <c r="E233" s="56" t="s">
+      <c r="A233" s="73"/>
+      <c r="B233" s="73"/>
+      <c r="C233" s="73"/>
+      <c r="D233" s="73"/>
+      <c r="E233" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="F233" s="56"/>
-      <c r="G233" s="56"/>
-      <c r="H233" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I233" s="60"/>
-      <c r="J233" s="73">
+      <c r="F233" s="66"/>
+      <c r="G233" s="66"/>
+      <c r="H233" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I233" s="70"/>
+      <c r="J233" s="71">
         <f>J229</f>
         <v>1000</v>
       </c>
-      <c r="K233" s="73"/>
-      <c r="L233" s="73"/>
-      <c r="M233" s="73">
+      <c r="K233" s="71"/>
+      <c r="L233" s="71"/>
+      <c r="M233" s="71">
         <f>M231</f>
         <v>200</v>
       </c>
-      <c r="N233" s="73"/>
-      <c r="O233" s="73"/>
+      <c r="N233" s="71"/>
+      <c r="O233" s="71"/>
     </row>
     <row r="234" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A234" s="53"/>
-      <c r="B234" s="54"/>
-      <c r="C234" s="54"/>
-      <c r="D234" s="55"/>
-      <c r="E234" s="57"/>
-      <c r="F234" s="58"/>
-      <c r="G234" s="59"/>
-      <c r="H234" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I234" s="60"/>
-      <c r="J234" s="73">
+      <c r="A234" s="74"/>
+      <c r="B234" s="75"/>
+      <c r="C234" s="75"/>
+      <c r="D234" s="76"/>
+      <c r="E234" s="67"/>
+      <c r="F234" s="68"/>
+      <c r="G234" s="69"/>
+      <c r="H234" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I234" s="70"/>
+      <c r="J234" s="71">
         <f>J230</f>
         <v>5</v>
       </c>
-      <c r="K234" s="73"/>
-      <c r="L234" s="73"/>
-      <c r="M234" s="73">
+      <c r="K234" s="71"/>
+      <c r="L234" s="71"/>
+      <c r="M234" s="71">
         <f>M232</f>
         <v>1</v>
       </c>
-      <c r="N234" s="73"/>
-      <c r="O234" s="73"/>
+      <c r="N234" s="71"/>
+      <c r="O234" s="71"/>
     </row>
     <row r="235" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A235" s="52"/>
-      <c r="B235" s="52"/>
-      <c r="C235" s="52"/>
-      <c r="D235" s="52"/>
-      <c r="E235" s="56" t="s">
+      <c r="A235" s="73"/>
+      <c r="B235" s="73"/>
+      <c r="C235" s="73"/>
+      <c r="D235" s="73"/>
+      <c r="E235" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="F235" s="56"/>
-      <c r="G235" s="56"/>
-      <c r="H235" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="I235" s="60"/>
-      <c r="J235" s="61">
+      <c r="F235" s="66"/>
+      <c r="G235" s="66"/>
+      <c r="H235" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="I235" s="70"/>
+      <c r="J235" s="94">
         <f>J227+J233-M233</f>
         <v>20800</v>
       </c>
-      <c r="K235" s="61"/>
-      <c r="L235" s="61"/>
+      <c r="K235" s="94"/>
+      <c r="L235" s="94"/>
       <c r="M235" s="8"/>
       <c r="N235" s="9"/>
       <c r="O235" s="10"/>
     </row>
     <row r="236" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A236" s="53"/>
-      <c r="B236" s="54"/>
-      <c r="C236" s="54"/>
-      <c r="D236" s="55"/>
-      <c r="E236" s="57"/>
-      <c r="F236" s="58"/>
-      <c r="G236" s="59"/>
-      <c r="H236" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="I236" s="60"/>
-      <c r="J236" s="61">
+      <c r="A236" s="74"/>
+      <c r="B236" s="75"/>
+      <c r="C236" s="75"/>
+      <c r="D236" s="76"/>
+      <c r="E236" s="67"/>
+      <c r="F236" s="68"/>
+      <c r="G236" s="69"/>
+      <c r="H236" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I236" s="70"/>
+      <c r="J236" s="94">
         <f>J228+J234-M234</f>
         <v>104</v>
       </c>
-      <c r="K236" s="61"/>
-      <c r="L236" s="61"/>
+      <c r="K236" s="94"/>
+      <c r="L236" s="94"/>
       <c r="M236" s="8"/>
       <c r="N236" s="9"/>
       <c r="O236" s="10"/>
@@ -2743,352 +2693,199 @@
       <c r="B237" s="24"/>
       <c r="C237" s="24"/>
       <c r="D237" s="25"/>
-      <c r="E237" s="38" t="s">
+      <c r="E237" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="F237" s="38"/>
-      <c r="G237" s="38"/>
+      <c r="F237" s="95"/>
+      <c r="G237" s="95"/>
       <c r="H237" s="26"/>
       <c r="I237" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="J237" s="42">
+      <c r="J237" s="99">
         <f>K209+K217+K223+J233</f>
         <v>1000</v>
       </c>
-      <c r="K237" s="43"/>
-      <c r="L237" s="44"/>
-      <c r="M237" s="45">
+      <c r="K237" s="100"/>
+      <c r="L237" s="101"/>
+      <c r="M237" s="102">
         <f>N209+M217+N223+M233</f>
         <v>1200</v>
       </c>
-      <c r="N237" s="46"/>
-      <c r="O237" s="47"/>
+      <c r="N237" s="103"/>
+      <c r="O237" s="104"/>
     </row>
     <row r="238" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A238" s="23"/>
       <c r="B238" s="24"/>
       <c r="C238" s="24"/>
       <c r="D238" s="25"/>
-      <c r="E238" s="39"/>
-      <c r="F238" s="40"/>
-      <c r="G238" s="41"/>
+      <c r="E238" s="96"/>
+      <c r="F238" s="97"/>
+      <c r="G238" s="98"/>
       <c r="H238" s="26"/>
       <c r="I238" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J238" s="42">
+      <c r="J238" s="99">
         <f>K210+K218+K224+J234</f>
         <v>5</v>
       </c>
-      <c r="K238" s="43"/>
-      <c r="L238" s="44"/>
-      <c r="M238" s="45">
+      <c r="K238" s="100"/>
+      <c r="L238" s="101"/>
+      <c r="M238" s="102">
         <f>N210+M218+N224+M234</f>
         <v>6</v>
       </c>
-      <c r="N238" s="46"/>
-      <c r="O238" s="47"/>
+      <c r="N238" s="103"/>
+      <c r="O238" s="104"/>
     </row>
     <row r="239" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A239" s="23"/>
       <c r="B239" s="24"/>
       <c r="C239" s="24"/>
       <c r="D239" s="25"/>
-      <c r="E239" s="38" t="s">
+      <c r="E239" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="F239" s="38"/>
-      <c r="G239" s="38"/>
+      <c r="F239" s="95"/>
+      <c r="G239" s="95"/>
       <c r="H239" s="26"/>
       <c r="I239" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="J239" s="42">
+      <c r="J239" s="99">
         <f>J205+J237-M237</f>
         <v>23200</v>
       </c>
-      <c r="K239" s="43"/>
-      <c r="L239" s="44"/>
-      <c r="M239" s="48"/>
-      <c r="N239" s="46"/>
-      <c r="O239" s="47"/>
+      <c r="K239" s="100"/>
+      <c r="L239" s="101"/>
+      <c r="M239" s="105"/>
+      <c r="N239" s="103"/>
+      <c r="O239" s="104"/>
     </row>
     <row r="240" spans="1:15" ht="10.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
       <c r="A240" s="23"/>
       <c r="B240" s="24"/>
       <c r="C240" s="24"/>
       <c r="D240" s="25"/>
-      <c r="E240" s="39"/>
-      <c r="F240" s="40"/>
-      <c r="G240" s="41"/>
+      <c r="E240" s="96"/>
+      <c r="F240" s="97"/>
+      <c r="G240" s="98"/>
       <c r="H240" s="26"/>
       <c r="I240" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J240" s="42">
+      <c r="J240" s="99">
         <f>J206+J238-M238</f>
         <v>116</v>
       </c>
-      <c r="K240" s="43"/>
-      <c r="L240" s="44"/>
-      <c r="M240" s="49"/>
-      <c r="N240" s="50"/>
-      <c r="O240" s="51"/>
+      <c r="K240" s="100"/>
+      <c r="L240" s="101"/>
+      <c r="M240" s="106"/>
+      <c r="N240" s="107"/>
+      <c r="O240" s="108"/>
     </row>
     <row r="241" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="30"/>
-      <c r="B241" s="30"/>
-      <c r="C241" s="30"/>
-      <c r="D241" s="30"/>
-      <c r="E241" s="34" t="s">
+      <c r="A241" s="110"/>
+      <c r="B241" s="110"/>
+      <c r="C241" s="110"/>
+      <c r="D241" s="110"/>
+      <c r="E241" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F241" s="34"/>
-      <c r="G241" s="34"/>
-      <c r="H241" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="I241" s="29"/>
-      <c r="J241" s="28">
+      <c r="F241" s="43"/>
+      <c r="G241" s="43"/>
+      <c r="H241" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="I241" s="47"/>
+      <c r="J241" s="109">
         <f>K201+J237</f>
         <v>1000</v>
       </c>
-      <c r="K241" s="28"/>
-      <c r="L241" s="28"/>
-      <c r="M241" s="28">
+      <c r="K241" s="109"/>
+      <c r="L241" s="109"/>
+      <c r="M241" s="109">
         <f>N201+M237</f>
         <v>1200</v>
       </c>
-      <c r="N241" s="28"/>
-      <c r="O241" s="28"/>
+      <c r="N241" s="109"/>
+      <c r="O241" s="109"/>
     </row>
     <row r="242" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="31"/>
-      <c r="B242" s="32"/>
-      <c r="C242" s="32"/>
-      <c r="D242" s="33"/>
-      <c r="E242" s="35"/>
-      <c r="F242" s="36"/>
-      <c r="G242" s="37"/>
-      <c r="H242" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="I242" s="29"/>
-      <c r="J242" s="28">
+      <c r="A242" s="111"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="113"/>
+      <c r="E242" s="44"/>
+      <c r="F242" s="45"/>
+      <c r="G242" s="46"/>
+      <c r="H242" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I242" s="47"/>
+      <c r="J242" s="109">
         <f>K202+J238</f>
         <v>5</v>
       </c>
-      <c r="K242" s="28"/>
-      <c r="L242" s="28"/>
-      <c r="M242" s="28">
+      <c r="K242" s="109"/>
+      <c r="L242" s="109"/>
+      <c r="M242" s="109">
         <f>N202+M238</f>
         <v>6</v>
       </c>
-      <c r="N242" s="28"/>
-      <c r="O242" s="28"/>
+      <c r="N242" s="109"/>
+      <c r="O242" s="109"/>
     </row>
     <row r="243" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="30"/>
-      <c r="B243" s="30"/>
-      <c r="C243" s="30"/>
-      <c r="D243" s="30"/>
-      <c r="E243" s="34" t="s">
+      <c r="A243" s="110"/>
+      <c r="B243" s="110"/>
+      <c r="C243" s="110"/>
+      <c r="D243" s="110"/>
+      <c r="E243" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F243" s="34"/>
-      <c r="G243" s="34"/>
-      <c r="H243" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="I243" s="29"/>
-      <c r="J243" s="28">
+      <c r="F243" s="43"/>
+      <c r="G243" s="43"/>
+      <c r="H243" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="I243" s="47"/>
+      <c r="J243" s="109">
         <f>J191+J241-M241</f>
         <v>23350</v>
       </c>
-      <c r="K243" s="28"/>
-      <c r="L243" s="28"/>
+      <c r="K243" s="109"/>
+      <c r="L243" s="109"/>
       <c r="M243" s="20"/>
       <c r="N243" s="21"/>
       <c r="O243" s="22"/>
     </row>
     <row r="244" spans="1:15" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="31"/>
-      <c r="B244" s="32"/>
-      <c r="C244" s="32"/>
-      <c r="D244" s="33"/>
-      <c r="E244" s="35"/>
-      <c r="F244" s="36"/>
-      <c r="G244" s="37"/>
-      <c r="H244" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="I244" s="29"/>
-      <c r="J244" s="28">
+      <c r="A244" s="111"/>
+      <c r="B244" s="112"/>
+      <c r="C244" s="112"/>
+      <c r="D244" s="113"/>
+      <c r="E244" s="44"/>
+      <c r="F244" s="45"/>
+      <c r="G244" s="46"/>
+      <c r="H244" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="I244" s="47"/>
+      <c r="J244" s="109">
         <f>J192+J242-M242</f>
         <v>126</v>
       </c>
-      <c r="K244" s="28"/>
-      <c r="L244" s="28"/>
+      <c r="K244" s="109"/>
+      <c r="L244" s="109"/>
       <c r="M244" s="20"/>
       <c r="N244" s="21"/>
       <c r="O244" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="167">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="E188:G190"/>
-    <mergeCell ref="H188:I190"/>
-    <mergeCell ref="J188:L190"/>
-    <mergeCell ref="M188:O190"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A191:D192"/>
-    <mergeCell ref="E191:G192"/>
-    <mergeCell ref="H191:I191"/>
-    <mergeCell ref="J191:L191"/>
-    <mergeCell ref="H192:I192"/>
-    <mergeCell ref="J192:L192"/>
-    <mergeCell ref="A193:D194"/>
-    <mergeCell ref="E193:G194"/>
-    <mergeCell ref="H193:I193"/>
-    <mergeCell ref="J193:L193"/>
-    <mergeCell ref="H194:I194"/>
-    <mergeCell ref="J194:L194"/>
-    <mergeCell ref="A195:D196"/>
-    <mergeCell ref="E195:G196"/>
-    <mergeCell ref="H195:I195"/>
-    <mergeCell ref="J195:L195"/>
-    <mergeCell ref="H196:I196"/>
-    <mergeCell ref="J196:L196"/>
-    <mergeCell ref="A197:D198"/>
-    <mergeCell ref="E197:G198"/>
-    <mergeCell ref="H197:I197"/>
-    <mergeCell ref="H198:I198"/>
-    <mergeCell ref="A199:D200"/>
-    <mergeCell ref="E199:G200"/>
-    <mergeCell ref="H199:I199"/>
-    <mergeCell ref="J199:L199"/>
-    <mergeCell ref="H200:I200"/>
-    <mergeCell ref="J200:L200"/>
-    <mergeCell ref="A201:D202"/>
-    <mergeCell ref="E201:G202"/>
-    <mergeCell ref="H201:I201"/>
-    <mergeCell ref="H202:I202"/>
-    <mergeCell ref="A203:D204"/>
-    <mergeCell ref="E203:G204"/>
-    <mergeCell ref="H203:I203"/>
-    <mergeCell ref="J203:L203"/>
-    <mergeCell ref="H204:I204"/>
-    <mergeCell ref="J204:L204"/>
-    <mergeCell ref="A205:D206"/>
-    <mergeCell ref="E205:G206"/>
-    <mergeCell ref="H205:I205"/>
-    <mergeCell ref="J205:L205"/>
-    <mergeCell ref="H206:I206"/>
-    <mergeCell ref="J206:L206"/>
-    <mergeCell ref="A207:D208"/>
-    <mergeCell ref="E207:G208"/>
-    <mergeCell ref="H207:I207"/>
-    <mergeCell ref="J207:L207"/>
-    <mergeCell ref="H208:I208"/>
-    <mergeCell ref="J208:L208"/>
-    <mergeCell ref="A209:D210"/>
-    <mergeCell ref="E209:G210"/>
-    <mergeCell ref="H209:I209"/>
-    <mergeCell ref="H210:I210"/>
-    <mergeCell ref="A211:D212"/>
-    <mergeCell ref="E211:G212"/>
-    <mergeCell ref="H211:I211"/>
-    <mergeCell ref="J211:L211"/>
-    <mergeCell ref="H212:I212"/>
-    <mergeCell ref="J212:L212"/>
-    <mergeCell ref="A213:D214"/>
-    <mergeCell ref="E213:G214"/>
-    <mergeCell ref="H213:I213"/>
-    <mergeCell ref="J213:L213"/>
-    <mergeCell ref="H214:I214"/>
-    <mergeCell ref="J214:L214"/>
-    <mergeCell ref="A215:D216"/>
-    <mergeCell ref="E215:G216"/>
-    <mergeCell ref="H215:I215"/>
-    <mergeCell ref="M215:O215"/>
-    <mergeCell ref="H216:I216"/>
-    <mergeCell ref="M216:O216"/>
-    <mergeCell ref="A217:D218"/>
-    <mergeCell ref="E217:G218"/>
-    <mergeCell ref="H217:I217"/>
-    <mergeCell ref="M217:O217"/>
-    <mergeCell ref="H218:I218"/>
-    <mergeCell ref="M218:O218"/>
-    <mergeCell ref="A219:D220"/>
-    <mergeCell ref="E219:G220"/>
-    <mergeCell ref="H219:I219"/>
-    <mergeCell ref="J219:L219"/>
-    <mergeCell ref="H220:I220"/>
-    <mergeCell ref="J220:L220"/>
-    <mergeCell ref="A221:D222"/>
-    <mergeCell ref="E221:G222"/>
-    <mergeCell ref="H221:I221"/>
-    <mergeCell ref="J221:L221"/>
-    <mergeCell ref="H222:I222"/>
-    <mergeCell ref="J222:L222"/>
-    <mergeCell ref="A223:D224"/>
-    <mergeCell ref="E223:G224"/>
-    <mergeCell ref="H223:I223"/>
-    <mergeCell ref="H224:I224"/>
-    <mergeCell ref="A225:D226"/>
-    <mergeCell ref="E225:G226"/>
-    <mergeCell ref="H225:I225"/>
-    <mergeCell ref="J225:L225"/>
-    <mergeCell ref="H226:I226"/>
-    <mergeCell ref="J226:L226"/>
-    <mergeCell ref="A227:D228"/>
-    <mergeCell ref="E227:G228"/>
-    <mergeCell ref="H227:I227"/>
-    <mergeCell ref="J227:L227"/>
-    <mergeCell ref="H228:I228"/>
-    <mergeCell ref="J228:L228"/>
-    <mergeCell ref="A229:D230"/>
-    <mergeCell ref="E229:G230"/>
-    <mergeCell ref="H229:I229"/>
-    <mergeCell ref="J229:L229"/>
-    <mergeCell ref="H230:I230"/>
-    <mergeCell ref="J230:L230"/>
-    <mergeCell ref="M231:O231"/>
-    <mergeCell ref="H232:I232"/>
-    <mergeCell ref="M232:O232"/>
-    <mergeCell ref="A233:D234"/>
-    <mergeCell ref="E233:G234"/>
-    <mergeCell ref="H233:I233"/>
-    <mergeCell ref="J233:L233"/>
-    <mergeCell ref="M233:O233"/>
-    <mergeCell ref="H234:I234"/>
-    <mergeCell ref="J234:L234"/>
-    <mergeCell ref="M234:O234"/>
-    <mergeCell ref="A235:D236"/>
-    <mergeCell ref="E235:G236"/>
-    <mergeCell ref="H235:I235"/>
-    <mergeCell ref="J235:L235"/>
-    <mergeCell ref="H236:I236"/>
-    <mergeCell ref="J236:L236"/>
-    <mergeCell ref="A231:D232"/>
-    <mergeCell ref="E231:G232"/>
-    <mergeCell ref="H231:I231"/>
-    <mergeCell ref="E237:G238"/>
-    <mergeCell ref="J237:L237"/>
-    <mergeCell ref="M237:O237"/>
-    <mergeCell ref="J238:L238"/>
-    <mergeCell ref="M238:O238"/>
-    <mergeCell ref="E239:G240"/>
-    <mergeCell ref="J239:L239"/>
-    <mergeCell ref="J240:L240"/>
-    <mergeCell ref="M239:O239"/>
-    <mergeCell ref="M240:O240"/>
     <mergeCell ref="M241:O241"/>
     <mergeCell ref="H242:I242"/>
     <mergeCell ref="J242:L242"/>
@@ -3103,9 +2900,162 @@
     <mergeCell ref="E241:G242"/>
     <mergeCell ref="H241:I241"/>
     <mergeCell ref="J241:L241"/>
+    <mergeCell ref="E237:G238"/>
+    <mergeCell ref="J237:L237"/>
+    <mergeCell ref="M237:O237"/>
+    <mergeCell ref="J238:L238"/>
+    <mergeCell ref="M238:O238"/>
+    <mergeCell ref="E239:G240"/>
+    <mergeCell ref="J239:L239"/>
+    <mergeCell ref="J240:L240"/>
+    <mergeCell ref="M239:O239"/>
+    <mergeCell ref="M240:O240"/>
+    <mergeCell ref="A235:D236"/>
+    <mergeCell ref="E235:G236"/>
+    <mergeCell ref="H235:I235"/>
+    <mergeCell ref="J235:L235"/>
+    <mergeCell ref="H236:I236"/>
+    <mergeCell ref="J236:L236"/>
+    <mergeCell ref="A231:D232"/>
+    <mergeCell ref="E231:G232"/>
+    <mergeCell ref="H231:I231"/>
+    <mergeCell ref="M231:O231"/>
+    <mergeCell ref="H232:I232"/>
+    <mergeCell ref="M232:O232"/>
+    <mergeCell ref="A233:D234"/>
+    <mergeCell ref="E233:G234"/>
+    <mergeCell ref="H233:I233"/>
+    <mergeCell ref="J233:L233"/>
+    <mergeCell ref="M233:O233"/>
+    <mergeCell ref="H234:I234"/>
+    <mergeCell ref="J234:L234"/>
+    <mergeCell ref="M234:O234"/>
+    <mergeCell ref="A227:D228"/>
+    <mergeCell ref="E227:G228"/>
+    <mergeCell ref="H227:I227"/>
+    <mergeCell ref="J227:L227"/>
+    <mergeCell ref="H228:I228"/>
+    <mergeCell ref="J228:L228"/>
+    <mergeCell ref="A229:D230"/>
+    <mergeCell ref="E229:G230"/>
+    <mergeCell ref="H229:I229"/>
+    <mergeCell ref="J229:L229"/>
+    <mergeCell ref="H230:I230"/>
+    <mergeCell ref="J230:L230"/>
+    <mergeCell ref="A223:D224"/>
+    <mergeCell ref="E223:G224"/>
+    <mergeCell ref="H223:I223"/>
+    <mergeCell ref="H224:I224"/>
+    <mergeCell ref="A225:D226"/>
+    <mergeCell ref="E225:G226"/>
+    <mergeCell ref="H225:I225"/>
+    <mergeCell ref="J225:L225"/>
+    <mergeCell ref="H226:I226"/>
+    <mergeCell ref="J226:L226"/>
+    <mergeCell ref="A219:D220"/>
+    <mergeCell ref="E219:G220"/>
+    <mergeCell ref="H219:I219"/>
+    <mergeCell ref="J219:L219"/>
+    <mergeCell ref="H220:I220"/>
+    <mergeCell ref="J220:L220"/>
+    <mergeCell ref="A221:D222"/>
+    <mergeCell ref="E221:G222"/>
+    <mergeCell ref="H221:I221"/>
+    <mergeCell ref="J221:L221"/>
+    <mergeCell ref="H222:I222"/>
+    <mergeCell ref="J222:L222"/>
+    <mergeCell ref="A215:D216"/>
+    <mergeCell ref="E215:G216"/>
+    <mergeCell ref="H215:I215"/>
+    <mergeCell ref="M215:O215"/>
+    <mergeCell ref="H216:I216"/>
+    <mergeCell ref="M216:O216"/>
+    <mergeCell ref="A217:D218"/>
+    <mergeCell ref="E217:G218"/>
+    <mergeCell ref="H217:I217"/>
+    <mergeCell ref="M217:O217"/>
+    <mergeCell ref="H218:I218"/>
+    <mergeCell ref="M218:O218"/>
+    <mergeCell ref="A211:D212"/>
+    <mergeCell ref="E211:G212"/>
+    <mergeCell ref="H211:I211"/>
+    <mergeCell ref="J211:L211"/>
+    <mergeCell ref="H212:I212"/>
+    <mergeCell ref="J212:L212"/>
+    <mergeCell ref="A213:D214"/>
+    <mergeCell ref="E213:G214"/>
+    <mergeCell ref="H213:I213"/>
+    <mergeCell ref="J213:L213"/>
+    <mergeCell ref="H214:I214"/>
+    <mergeCell ref="J214:L214"/>
+    <mergeCell ref="A207:D208"/>
+    <mergeCell ref="E207:G208"/>
+    <mergeCell ref="H207:I207"/>
+    <mergeCell ref="J207:L207"/>
+    <mergeCell ref="H208:I208"/>
+    <mergeCell ref="J208:L208"/>
+    <mergeCell ref="A209:D210"/>
+    <mergeCell ref="E209:G210"/>
+    <mergeCell ref="H209:I209"/>
+    <mergeCell ref="H210:I210"/>
+    <mergeCell ref="A203:D204"/>
+    <mergeCell ref="E203:G204"/>
+    <mergeCell ref="H203:I203"/>
+    <mergeCell ref="J203:L203"/>
+    <mergeCell ref="H204:I204"/>
+    <mergeCell ref="J204:L204"/>
+    <mergeCell ref="A205:D206"/>
+    <mergeCell ref="E205:G206"/>
+    <mergeCell ref="H205:I205"/>
+    <mergeCell ref="J205:L205"/>
+    <mergeCell ref="H206:I206"/>
+    <mergeCell ref="J206:L206"/>
+    <mergeCell ref="A199:D200"/>
+    <mergeCell ref="E199:G200"/>
+    <mergeCell ref="H199:I199"/>
+    <mergeCell ref="J199:L199"/>
+    <mergeCell ref="H200:I200"/>
+    <mergeCell ref="J200:L200"/>
+    <mergeCell ref="A201:D202"/>
+    <mergeCell ref="E201:G202"/>
+    <mergeCell ref="H201:I201"/>
+    <mergeCell ref="H202:I202"/>
+    <mergeCell ref="A195:D196"/>
+    <mergeCell ref="E195:G196"/>
+    <mergeCell ref="H195:I195"/>
+    <mergeCell ref="J195:L195"/>
+    <mergeCell ref="H196:I196"/>
+    <mergeCell ref="J196:L196"/>
+    <mergeCell ref="A197:D198"/>
+    <mergeCell ref="E197:G198"/>
+    <mergeCell ref="H197:I197"/>
+    <mergeCell ref="H198:I198"/>
+    <mergeCell ref="A191:D192"/>
+    <mergeCell ref="E191:G192"/>
+    <mergeCell ref="H191:I191"/>
+    <mergeCell ref="J191:L191"/>
+    <mergeCell ref="H192:I192"/>
+    <mergeCell ref="J192:L192"/>
+    <mergeCell ref="A193:D194"/>
+    <mergeCell ref="E193:G194"/>
+    <mergeCell ref="H193:I193"/>
+    <mergeCell ref="J193:L193"/>
+    <mergeCell ref="H194:I194"/>
+    <mergeCell ref="J194:L194"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:R4"/>
+    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="E188:G190"/>
+    <mergeCell ref="H188:I190"/>
+    <mergeCell ref="J188:L190"/>
+    <mergeCell ref="M188:O190"/>
+    <mergeCell ref="A189:D189"/>
+    <mergeCell ref="A190:D190"/>
   </mergeCells>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>